--- a/product/finance/ucm/output/model.xlsx
+++ b/product/finance/ucm/output/model.xlsx
@@ -8658,7 +8658,7 @@
         <v>-250146.71</v>
       </c>
       <c r="C3" s="4">
-        <v>598083.2</v>
+        <v>601083.2</v>
       </c>
       <c r="D3" s="4">
         <v>-740217</v>
@@ -8672,7 +8672,7 @@
         <v>382825.5</v>
       </c>
       <c r="C4" s="4">
-        <v>280022.76</v>
+        <v>278522.76</v>
       </c>
       <c r="D4" s="4">
         <v>740217</v>
@@ -10098,7 +10098,7 @@
         <v>950</v>
       </c>
       <c r="E15" s="5">
-        <f>CHOOSE(MATCH(ScenarioSelector,{"Base","Upside","Downside"},0),147,12346,0)</f>
+        <f>CHOOSE(MATCH(ScenarioSelector,{"Base","Upside","Downside"},0),147,10846,0)</f>
         <v>147</v>
       </c>
       <c r="F15" s="5">
